--- a/out/Attention-Mamba1_repeat_3_000005.xlsx
+++ b/out/Attention-Mamba1_repeat_3_000005.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-4.806964148813838</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.1348825055873001</v>
+        <v>1.462243845257878</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.7348825055873001</v>
+        <v>1.462243845257878</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.7348825055873001</v>
+        <v>1.462243845257878</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.7348825055873001</v>
+        <v>1.462243845257878</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.7348825055873001</v>
+        <v>1.462243845257878</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-4.806964148813838</v>
+        <v>1.462243845257878</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.1348825055873001</v>
+        <v>1.462243845257878</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-4.806964148813838</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-4.806964148813838</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-4.806964148813838</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-4.806964148813838</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-4.806964148813838</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-4.806964148813838</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-4.806964148813838</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-4.806964148813838</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.8622438452578782</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83617,14 +83617,14 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84412,14 +84412,14 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.1348825055873001</v>
+        <v>1.462243845257878</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.386393030374176</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.1348825055873001</v>
+        <v>1.462243845257878</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93952,14 +93952,14 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.386393030374176</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.1348825055873001</v>
+        <v>1.462243845257878</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.386393030374176</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.386393030374176</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97132,14 +97132,14 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.986393030374176</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.1348825055873001</v>
+        <v>1.462243845257878</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-4.806964148813838</v>
+        <v>-1.386393030374176</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.386393030374176</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-Mamba1_repeat_3_000005.xlsx
+++ b/out/Attention-Mamba1_repeat_3_000005.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-4.806964148813838</v>
+        <v>-1.330897426655783</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.1348825055873001</v>
+        <v>-0.8011965688743772</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.7348825055873001</v>
+        <v>-0.8011965688743772</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-4.806964148813838</v>
+        <v>-0.8011965688743772</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.1348825055873001</v>
+        <v>-0.8011965688743772</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.1348825055873001</v>
+        <v>-0.8011965688743772</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-4.806964148813838</v>
+        <v>-0.8011965688743772</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.860598284437189</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-4.806964148813838</v>
+        <v>-1.860598284437189</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-4.806964148813838</v>
+        <v>-1.860598284437189</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.1348825055873001</v>
+        <v>-0.8011965688743772</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.7348825055873001</v>
+        <v>-0.6011965688743771</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-4.806964148813838</v>
+        <v>-1.860598284437189</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-4.806964148813838</v>
+        <v>-2.92</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-4.806964148813838</v>
+        <v>-1.860598284437189</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.860598284437189</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-4.806964148813838</v>
+        <v>-0.8011965688743772</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.7348825055873001</v>
+        <v>-0.8011965688743772</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.1348825055873001</v>
+        <v>-0.8011965688743772</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-4.806964148813838</v>
+        <v>-0.8011965688743772</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.1348825055873001</v>
+        <v>-0.8011965688743772</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.7348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.4582051466884344</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.1348825055873001</v>
+        <v>0.2582051466884343</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.1348825055873001</v>
+        <v>-0.8011965688743772</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-4.806964148813838</v>
+        <v>-0.8011965688743772</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.1348825055873001</v>
+        <v>-1.330897426655783</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-Mamba1_repeat_3_000005.xlsx
+++ b/out/Attention-Mamba1_repeat_3_000005.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.0003035962581634521</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.330897426655783</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.0007098019123077393</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.8011965688743772</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.001158822327852249</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.0007307901978492737</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.0002443268895149231</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.4582051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.000994313508272171</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.4582051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.001427315175533295</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.8011965688743772</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.0002672187983989716</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.8011965688743772</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.0004506483674049377</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8011965688743772</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.0003354363143444061</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.00107182189822197</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.4582051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.0005729049444198608</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.4582051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.001011684536933899</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.4582051466884344</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.0008298382163047791</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.4582051466884344</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.001000788062810898</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.4582051466884344</v>
+        <v>0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.00215945765376091</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.4582051466884344</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.001680310815572739</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.4582051466884344</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.004335988312959671</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.8011965688743772</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.0001386292278766632</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.8011965688743772</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.004238694906234741</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.860598284437189</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.0002141445875167847</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.860598284437189</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.001666106283664703</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.860598284437189</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>8.402392268180847e-05</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.8011965688743772</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.001296356320381165</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.0007244609296321869</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.4582051466884344</v>
+        <v>-0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.0005643963813781738</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.4582051466884344</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.0009989887475967407</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.4582051466884344</v>
+        <v>0.16</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.0004133805632591248</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.4582051466884344</v>
+        <v>0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.0007320977747440338</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.4582051466884344</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.001598645001649857</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.4582051466884344</v>
+        <v>0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.006687473505735397</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.6011965688743771</v>
+        <v>0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.001502815634012222</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.860598284437189</v>
+        <v>0.16</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.001038830727338791</v>
       </c>
       <c r="JB34" t="n">
-        <v>-2.92</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.0002516955137252808</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.860598284437189</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.0003552734851837158</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.860598284437189</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.0002926141023635864</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.8011965688743772</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.0008670873939990997</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.8011965688743772</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.001126285642385483</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.4582051466884344</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.0003312267363071442</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.4582051466884344</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.0009588152170181274</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.4582051466884344</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.0005581118166446686</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.4582051466884344</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.0006968788802623749</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.4582051466884344</v>
+        <v>0.16</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.0009108148515224457</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.4582051466884344</v>
+        <v>0.16</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.0006008371710777283</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.4582051466884344</v>
+        <v>0.3</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.001105107367038727</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.4582051466884344</v>
+        <v>0.3</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.000886332243680954</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.4582051466884344</v>
+        <v>0.3</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.000860121101140976</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.3</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.0007295534014701843</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.3</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.0006678663194179535</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41486,10 +41486,10 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.000998321920633316</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.001465305685997009</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.001057684421539307</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.0008228346705436707</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.001237828284502029</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.000605408102273941</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.001910772174596786</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.8011965688743772</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-5.510449409484863e-05</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.8011965688743772</v>
+        <v>-0.3</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.0009616613388061523</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.8011965688743772</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.0007570907473564148</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.0002587698400020599</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.0001589506864547729</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.4582051466884344</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.000692468136548996</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.4582051466884344</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51821,10 +51821,10 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.001119785010814667</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.4582051466884344</v>
+        <v>-0.16</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.001102428883314133</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.4582051466884344</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.001372117549180984</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.4582051466884344</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.001447148621082306</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.4582051466884344</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.0009764283895492554</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.4582051466884344</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55796,10 +55796,10 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.001054048538208008</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.001118991523981094</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.3</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57386,10 +57386,10 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.000574406236410141</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.16</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.0006195008754730225</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.001768987625837326</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.008054155856370926</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.001328151673078537</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.01401077583432198</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.005271177738904953</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.003840390592813492</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.000888485461473465</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.002006862312555313</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.3</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.002589348703622818</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.3</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.002435408532619476</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.16</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.004764627665281296</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.002103753387928009</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.004216767847537994</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.002017758786678314</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.003652617335319519</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.007302850484848022</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.002466097474098206</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.0006569065153598785</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.0009911954402923584</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.002499029040336609</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.001940548419952393</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.00334644690155983</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.16</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.003215309232473373</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.3</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.004252858459949493</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.3</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.001764703541994095</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.002130135893821716</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.0025162473320961</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.002582471817731857</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.002468172460794449</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.004863306879997253</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.002272065728902817</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.3</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.002916034311056137</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.00378786027431488</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.002745077013969421</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.3</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.002296172082424164</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.16</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.003036685287952423</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.002482440322637558</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.003434766083955765</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.003749974071979523</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.00475432351231575</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.006232418119907379</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.02301612682640553</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.004010099917650223</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.04134638234972954</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.01516608893871307</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.02680177055299282</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.2582051466884343</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.007291968911886215</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.16</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.002994701266288757</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97132,14 +97132,14 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.005706895142793655</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.3</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.02232377603650093</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.16</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.01426988840103149</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.2582051466884343</v>
+        <v>-0.16</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.0534166507422924</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.8011965688743772</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.005867518484592438</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.8011965688743772</v>
+        <v>-0.6500000000000004</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.003775849938392639</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.330897426655783</v>
+        <v>-1</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-Mamba1_repeat_3_000005.xlsx
+++ b/out/Attention-Mamba1_repeat_3_000005.xlsx
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.0007098019123077393</v>
+        <v>0.0007097832858562469</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.0007307901978492737</v>
+        <v>0.0007307641208171844</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.0002443268895149231</v>
+        <v>0.0002443194389343262</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.000994313508272171</v>
+        <v>0.0009943209588527679</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.0002672187983989716</v>
+        <v>-0.0002672150731086731</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.0004506483674049377</v>
+        <v>0.0004506520926952362</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.0003354363143444061</v>
+        <v>0.0003354325890541077</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.00107182189822197</v>
+        <v>0.001071836799383163</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.0005729049444198608</v>
+        <v>0.0005729161202907562</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.001011684536933899</v>
+        <v>0.001011665910482407</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.2599999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.0008298382163047791</v>
+        <v>0.0008298307657241821</v>
       </c>
       <c r="JB15" t="n">
         <v>0.02000000000000007</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.001000788062810898</v>
+        <v>0.001000799238681793</v>
       </c>
       <c r="JB16" t="n">
         <v>0.3</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.00215945765376091</v>
+        <v>0.002159491181373596</v>
       </c>
       <c r="JB17" t="n">
         <v>0.5799999999999998</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.001680310815572739</v>
+        <v>0.001680314540863037</v>
       </c>
       <c r="JB18" t="n">
         <v>0.5799999999999998</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.004335988312959671</v>
+        <v>0.004335951060056686</v>
       </c>
       <c r="JB19" t="n">
         <v>0.7199999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.0001386292278766632</v>
+        <v>-0.0001386329531669617</v>
       </c>
       <c r="JB20" t="n">
         <v>0.4399999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.004238694906234741</v>
+        <v>0.004238713532686234</v>
       </c>
       <c r="JB21" t="n">
         <v>0.1600000000000001</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.0002141445875167847</v>
+        <v>-0.0002141296863555908</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.7199999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.001666106283664703</v>
+        <v>-0.001666098833084106</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.4399999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>8.402392268180847e-05</v>
+        <v>8.401647210121155e-05</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.5799999999999998</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.001296356320381165</v>
+        <v>0.001296386122703552</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.4399999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.0007244609296321869</v>
+        <v>0.0007244646549224854</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.3</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.0005643963813781738</v>
+        <v>0.00056438148021698</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.3</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.0009989887475967407</v>
+        <v>0.0009989738464355469</v>
       </c>
       <c r="JB28" t="n">
         <v>0.16</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.0004133805632591248</v>
+        <v>0.0004134029150009155</v>
       </c>
       <c r="JB29" t="n">
         <v>0.3</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.0007320977747440338</v>
+        <v>0.0007320791482925415</v>
       </c>
       <c r="JB30" t="n">
         <v>0.4399999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.001598645001649857</v>
+        <v>0.001598697155714035</v>
       </c>
       <c r="JB31" t="n">
         <v>0.3</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.006687473505735397</v>
+        <v>0.006687484681606293</v>
       </c>
       <c r="JB32" t="n">
         <v>0.3</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.001038830727338791</v>
+        <v>-0.001038838177919388</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.7199999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.0002516955137252808</v>
+        <v>-0.0002516880631446838</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.9999999999999998</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.0003552734851837158</v>
+        <v>0.000355258584022522</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.8599999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.0002926141023635864</v>
+        <v>-0.000292602926492691</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.7199999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.0008670873939990997</v>
+        <v>0.0008670762181282043</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.7199999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.001126285642385483</v>
+        <v>0.001126263290643692</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.5799999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.0003312267363071442</v>
+        <v>0.0003312453627586365</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.5799999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.0009588152170181274</v>
+        <v>0.0009587928652763367</v>
       </c>
       <c r="JB41" t="n">
         <v>0.02000000000000007</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.0005581118166446686</v>
+        <v>0.000558122992515564</v>
       </c>
       <c r="JB42" t="n">
         <v>0.02000000000000007</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.0006968788802623749</v>
+        <v>0.0006969012320041656</v>
       </c>
       <c r="JB43" t="n">
         <v>0.16</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.0009108148515224457</v>
+        <v>0.000910785049200058</v>
       </c>
       <c r="JB44" t="n">
         <v>0.16</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.0006008371710777283</v>
+        <v>0.0006008073687553406</v>
       </c>
       <c r="JB45" t="n">
         <v>0.3</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.001105107367038727</v>
+        <v>0.001105066388845444</v>
       </c>
       <c r="JB46" t="n">
         <v>0.3</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.000886332243680954</v>
+        <v>0.0008863471448421478</v>
       </c>
       <c r="JB47" t="n">
         <v>0.3</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.000860121101140976</v>
+        <v>0.0008601322770118713</v>
       </c>
       <c r="JB48" t="n">
         <v>0.3</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.0007295534014701843</v>
+        <v>0.0007295124232769012</v>
       </c>
       <c r="JB49" t="n">
         <v>0.3</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.0006678663194179535</v>
+        <v>0.000667870044708252</v>
       </c>
       <c r="JB50" t="n">
         <v>0.4399999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.000998321920633316</v>
+        <v>0.0009982995688915253</v>
       </c>
       <c r="JB51" t="n">
         <v>0.4399999999999999</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.001465305685997009</v>
+        <v>0.00146527960896492</v>
       </c>
       <c r="JB52" t="n">
         <v>0.4399999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.001057684421539307</v>
+        <v>0.001057688146829605</v>
       </c>
       <c r="JB53" t="n">
         <v>0.5799999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.0008228346705436707</v>
+        <v>0.0008228123188018799</v>
       </c>
       <c r="JB54" t="n">
         <v>0.5799999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.000605408102273941</v>
+        <v>0.0006054267287254333</v>
       </c>
       <c r="JB56" t="n">
         <v>0.4399999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.001910772174596786</v>
+        <v>0.001910779625177383</v>
       </c>
       <c r="JB57" t="n">
         <v>0.4399999999999999</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-5.510449409484863e-05</v>
+        <v>-5.510821938514709e-05</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.3</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.0009616613388061523</v>
+        <v>0.000961650162935257</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.4399999999999999</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.0007570907473564148</v>
+        <v>0.0007570981979370117</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.7199999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.0002587698400020599</v>
+        <v>0.0002587810158729553</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.5799999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.0001589506864547729</v>
+        <v>0.0001589283347129822</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.4399999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.000692468136548996</v>
+        <v>0.0006924644112586975</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.4399999999999999</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.001102428883314133</v>
+        <v>0.001102406531572342</v>
       </c>
       <c r="JB65" t="n">
         <v>0.7199999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.001372117549180984</v>
+        <v>0.001372102648019791</v>
       </c>
       <c r="JB66" t="n">
         <v>0.7199999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.001447148621082306</v>
+        <v>0.001447182148694992</v>
       </c>
       <c r="JB67" t="n">
         <v>0.5799999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.0009764283895492554</v>
+        <v>0.0009764470160007477</v>
       </c>
       <c r="JB68" t="n">
         <v>0.5799999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.001054048538208008</v>
+        <v>0.001054055988788605</v>
       </c>
       <c r="JB69" t="n">
         <v>0.4399999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.001118991523981094</v>
+        <v>0.001118998974561691</v>
       </c>
       <c r="JB70" t="n">
         <v>0.3</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.000574406236410141</v>
+        <v>0.0005744099617004395</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.16</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.0006195008754730225</v>
+        <v>0.0006194934248924255</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.02000000000000007</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.001768987625837326</v>
+        <v>0.001769021153450012</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.02000000000000007</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.008054155856370926</v>
+        <v>0.008054137229919434</v>
       </c>
       <c r="JB74" t="n">
         <v>0.7199999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.001328151673078537</v>
+        <v>0.001328147947788239</v>
       </c>
       <c r="JB75" t="n">
         <v>0.8599999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.01401077583432198</v>
+        <v>0.01401077210903168</v>
       </c>
       <c r="JB76" t="n">
         <v>0.8599999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.005271177738904953</v>
+        <v>0.005271192640066147</v>
       </c>
       <c r="JB77" t="n">
         <v>0.5799999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.003840390592813492</v>
+        <v>0.00384039431810379</v>
       </c>
       <c r="JB78" t="n">
         <v>0.5799999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.000888485461473465</v>
+        <v>0.0008885040879249573</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.1600000000000001</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.002006862312555313</v>
+        <v>0.002006854861974716</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.3</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.002589348703622818</v>
+        <v>0.002589363604784012</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.3</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.002435408532619476</v>
+        <v>0.002435356378555298</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.16</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.004764627665281296</v>
+        <v>0.004764657467603683</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.02000000000000007</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.002103753387928009</v>
+        <v>0.002103768289089203</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.02000000000000007</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.004216767847537994</v>
+        <v>0.004216786473989487</v>
       </c>
       <c r="JB85" t="n">
         <v>0.7199999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.002017758786678314</v>
+        <v>0.002017773687839508</v>
       </c>
       <c r="JB86" t="n">
         <v>0.7199999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.003652617335319519</v>
+        <v>0.003652594983577728</v>
       </c>
       <c r="JB87" t="n">
         <v>0.7199999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.007302850484848022</v>
+        <v>0.00730283185839653</v>
       </c>
       <c r="JB88" t="n">
         <v>0.4399999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.002466097474098206</v>
+        <v>0.002466075122356415</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.3</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.0006569065153598785</v>
+        <v>0.0006569363176822662</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.4399999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.0009911954402923584</v>
+        <v>0.000991184264421463</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.7199999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.002499029040336609</v>
+        <v>0.002499036490917206</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.5799999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.001940548419952393</v>
+        <v>0.001940544694662094</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.4399999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.00334644690155983</v>
+        <v>0.003346458077430725</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.16</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.003215309232473373</v>
+        <v>0.00321529433131218</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.3</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.004252858459949493</v>
+        <v>0.004252851009368896</v>
       </c>
       <c r="JB96" t="n">
         <v>0.3</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.001764703541994095</v>
+        <v>0.001764699816703796</v>
       </c>
       <c r="JB97" t="n">
         <v>0.02000000000000007</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.002130135893821716</v>
+        <v>0.002130120992660522</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.7199999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.0025162473320961</v>
+        <v>0.002516243606805801</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.9999999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.002468172460794449</v>
+        <v>0.002468153834342957</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.7199999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.004863306879997253</v>
+        <v>0.004863344132900238</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.5799999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.002272065728902817</v>
+        <v>0.002272069454193115</v>
       </c>
       <c r="JB103" t="n">
         <v>0.3</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.002916034311056137</v>
+        <v>0.002916019409894943</v>
       </c>
       <c r="JB104" t="n">
         <v>0.4399999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.002745077013969421</v>
+        <v>0.002745065838098526</v>
       </c>
       <c r="JB106" t="n">
         <v>0.3</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.002296172082424164</v>
+        <v>0.002296134829521179</v>
       </c>
       <c r="JB107" t="n">
         <v>0.16</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.003036685287952423</v>
+        <v>0.003036726266145706</v>
       </c>
       <c r="JB108" t="n">
         <v>0.02000000000000007</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.002482440322637558</v>
+        <v>0.002482455223798752</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.4399999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.003434766083955765</v>
+        <v>0.003434754908084869</v>
       </c>
       <c r="JB110" t="n">
         <v>0.4399999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.00475432351231575</v>
+        <v>0.004754312336444855</v>
       </c>
       <c r="JB112" t="n">
         <v>0.8599999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.02301612682640553</v>
+        <v>0.02301614731550217</v>
       </c>
       <c r="JB114" t="n">
         <v>0.8599999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.004010099917650223</v>
+        <v>0.004010096192359924</v>
       </c>
       <c r="JB115" t="n">
         <v>0.8599999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.04134638234972954</v>
+        <v>0.04134637862443924</v>
       </c>
       <c r="JB116" t="n">
         <v>0.8599999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.01516608893871307</v>
+        <v>0.01516608148813248</v>
       </c>
       <c r="JB117" t="n">
         <v>0.7199999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.02680177055299282</v>
+        <v>0.02680178359150887</v>
       </c>
       <c r="JB118" t="n">
         <v>0.5799999999999998</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.007291968911886215</v>
+        <v>0.007291946560144424</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.16</v>
+        <v>-0.3</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.002994701266288757</v>
+        <v>0.002994690090417862</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.1600000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.005706895142793655</v>
+        <v>0.00570688396692276</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.02232377603650093</v>
+        <v>0.02232380770146847</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.16</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0.01426988840103149</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.16</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.0534166507422924</v>
+        <v>0.0534166544675827</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.3</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.005867518484592438</v>
+        <v>-0.005867552012205124</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.6500000000000004</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.003775849938392639</v>
+        <v>0.003775857388973236</v>
       </c>
       <c r="JB126" t="n">
         <v>-1</v>
